--- a/data/trans_dic/P36BPD01_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>97,46; 99,3</t>
+          <t>97,42; 99,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,57; 98,43</t>
+          <t>96,48; 98,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,34; 98,64</t>
+          <t>97,36; 98,61</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,18; 97,38</t>
+          <t>92,53; 97,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,55; 96,18</t>
+          <t>93,77; 96,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,64; 96,58</t>
+          <t>93,49; 96,51</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,89; 93,33</t>
+          <t>87,57; 93,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,16; 96,38</t>
+          <t>90,31; 96,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,22; 94,95</t>
+          <t>90,3; 94,98</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,69; 97,77</t>
+          <t>94,72; 97,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,41; 97,8</t>
+          <t>95,62; 97,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,59; 97,49</t>
+          <t>95,66; 97,51</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,22; 96,41</t>
+          <t>94,13; 96,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,88; 96,43</t>
+          <t>94,85; 96,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,8; 96,1</t>
+          <t>94,77; 96,15</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>619307; 630981</t>
+          <t>619059; 630808</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>652229; 664737</t>
+          <t>651629; 664311</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1275957; 1293039</t>
+          <t>1276170; 1292531</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1094650; 1156329</t>
+          <t>1098705; 1157599</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>894466; 919554</t>
+          <t>896589; 919432</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2007296; 2070345</t>
+          <t>2004031; 2068730</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>609686; 647379</t>
+          <t>607478; 645386</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>839067; 896889</t>
+          <t>840465; 898140</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1465487; 1542195</t>
+          <t>1466665; 1542820</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>876010; 904448</t>
+          <t>876321; 903671</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1043124; 1069226</t>
+          <t>1045416; 1069897</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1929408; 1967676</t>
+          <t>1930836; 1968208</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3242677; 3318017</t>
+          <t>3239663; 3314832</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3468372; 3524900</t>
+          <t>3467078; 3528030</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6728011; 6820115</t>
+          <t>6725947; 6823898</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD01_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>97,42; 99,27</t>
+          <t>96,47; 98,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,48; 98,36</t>
+          <t>96,08; 98,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,36; 98,61</t>
+          <t>96,8; 98,28</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,53; 97,48</t>
+          <t>90,08; 94,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,77; 96,16</t>
+          <t>93,94; 96,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,49; 96,51</t>
+          <t>92,54; 94,79</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,57; 93,04</t>
+          <t>87,29; 92,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,31; 96,51</t>
+          <t>87,12; 91,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,3; 94,98</t>
+          <t>88,34; 91,52</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,72; 97,68</t>
+          <t>93,48; 96,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,62; 97,86</t>
+          <t>94,43; 96,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,66; 97,51</t>
+          <t>94,47; 96,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,13; 96,31</t>
+          <t>92,76; 94,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,85; 96,52</t>
+          <t>93,79; 95,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,77; 96,15</t>
+          <t>93,5; 94,74</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>626659</t>
+          <t>677132</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>658936</t>
+          <t>712658</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1285595</t>
+          <t>1389790</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>619059; 630808</t>
+          <t>666317; 683595</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>651629; 664311</t>
+          <t>704022; 718656</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1276170; 1292531</t>
+          <t>1377886; 1398946</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1125749</t>
+          <t>963782</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>909731</t>
+          <t>1015987</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2035480</t>
+          <t>1979769</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1098705; 1157599</t>
+          <t>940178; 982856</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>896589; 919432</t>
+          <t>1003207; 1026464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2004031; 2068730</t>
+          <t>1954115; 2001553</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>630731</t>
+          <t>715525</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>865996</t>
+          <t>724886</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1496726</t>
+          <t>1440411</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>607478; 645386</t>
+          <t>692015; 732482</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>840465; 898140</t>
+          <t>705101; 741031</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1466665; 1542820</t>
+          <t>1415227; 1466231</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>893307</t>
+          <t>942177</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1059089</t>
+          <t>1070650</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1952396</t>
+          <t>2012827</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>876321; 903671</t>
+          <t>923905; 955266</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1045416; 1069897</t>
+          <t>1055029; 1082978</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1930836; 1968208</t>
+          <t>1989216; 2031042</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3276446</t>
+          <t>3298616</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3493752</t>
+          <t>3524181</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6770198</t>
+          <t>6822797</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3239663; 3314832</t>
+          <t>3260980; 3328952</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3467078; 3528030</t>
+          <t>3495998; 3551130</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6725947; 6823898</t>
+          <t>6771769; 6861831</t>
         </is>
       </c>
     </row>
